--- a/docentes/Velasco Sánchez David - Estadisticos 20222.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="63">
   <si>
     <t>Mat</t>
   </si>
@@ -85,13 +85,16 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CORONA</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
     <t>MAZAHUA</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
+    <t>REYES</t>
   </si>
   <si>
     <t>AMADOR</t>
@@ -106,6 +109,9 @@
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
     <t>VASQUEZ</t>
   </si>
   <si>
@@ -121,13 +127,16 @@
     <t>DE LOS SANTOS</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>JUAREZ</t>
   </si>
   <si>
     <t>TEXOCO</t>
   </si>
   <si>
-    <t>CONCHE</t>
+    <t>VINALAY</t>
   </si>
   <si>
     <t>PORRAS</t>
@@ -142,7 +151,7 @@
     <t>BELLO</t>
   </si>
   <si>
-    <t>PEREZ</t>
+    <t>GAMEZ</t>
   </si>
   <si>
     <t>MENDOZA</t>
@@ -157,13 +166,16 @@
     <t>CALIHUA</t>
   </si>
   <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
     <t>LUIS ANGEL</t>
   </si>
   <si>
     <t>OCTAVIO</t>
   </si>
   <si>
-    <t>GUSTAVO</t>
+    <t>ANGEL SAID</t>
   </si>
   <si>
     <t>FRANCISCO ALAN</t>
@@ -176,6 +188,9 @@
   </si>
   <si>
     <t>ZURIEL ARTURO</t>
+  </si>
+  <si>
+    <t>ABIUD</t>
   </si>
   <si>
     <t>GUILLERMO</t>
@@ -1115,7 +1130,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1147,16 +1162,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920013</v>
+        <v>20330051920362</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1170,16 +1185,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920021</v>
+        <v>20330051920013</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1193,22 +1208,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920039</v>
+        <v>20330051920021</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1216,22 +1231,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920040</v>
+        <v>20330051920060</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1239,16 +1254,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920046</v>
+        <v>20330051920040</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1262,16 +1277,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920365</v>
+        <v>20330051920046</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1285,19 +1300,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920058</v>
+        <v>20330051920365</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
         <v>15</v>
@@ -1308,19 +1323,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920112</v>
+        <v>20330051920058</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
         <v>15</v>
@@ -1331,68 +1346,68 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920028</v>
+        <v>20330051920111</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920226</v>
+        <v>20330051920112</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920240</v>
+        <v>21330051920028</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1400,16 +1415,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920251</v>
+        <v>20330051920226</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -1418,6 +1433,52 @@
         <v>13</v>
       </c>
       <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>20330051920240</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>20330051920251</v>
+      </c>
+      <c r="B15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Velasco Sánchez David - Estadisticos 20222.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="48">
   <si>
     <t>Mat</t>
   </si>
@@ -91,9 +91,6 @@
     <t>FLORES</t>
   </si>
   <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
     <t>REYES</t>
   </si>
   <si>
@@ -106,9 +103,6 @@
     <t>DIAZ</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>VALENTE</t>
   </si>
   <si>
@@ -118,24 +112,12 @@
     <t>TRUJILLO</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
     <t>JUAREZ</t>
   </si>
   <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
     <t>VINALAY</t>
   </si>
   <si>
@@ -148,33 +130,18 @@
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>BELLO</t>
-  </si>
-  <si>
     <t>GAMEZ</t>
   </si>
   <si>
     <t>MENDOZA</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
     <t>JOSUE</t>
   </si>
   <si>
     <t>LUIS ANGEL</t>
   </si>
   <si>
-    <t>OCTAVIO</t>
-  </si>
-  <si>
     <t>ANGEL SAID</t>
   </si>
   <si>
@@ -187,9 +154,6 @@
     <t>BRUNO AZAEL</t>
   </si>
   <si>
-    <t>ZURIEL ARTURO</t>
-  </si>
-  <si>
     <t>ABIUD</t>
   </si>
   <si>
@@ -197,15 +161,6 @@
   </si>
   <si>
     <t>JAFET</t>
-  </si>
-  <si>
-    <t>JESSICA</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>ANGEL EMMANUEL</t>
   </si>
 </sst>
 </file>
@@ -824,16 +779,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="H3">
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -847,16 +805,19 @@
         <v>34</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>34</v>
       </c>
-      <c r="E4">
-        <v>34</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -893,16 +854,19 @@
         <v>28</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>71.43000000000001</v>
+      </c>
+      <c r="H6">
+        <v>6.7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -916,16 +880,19 @@
         <v>28</v>
       </c>
       <c r="D7">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>92.86</v>
+      </c>
+      <c r="H7">
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -1007,16 +974,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>76.67</v>
+        <v>80</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1033,16 +1000,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G4">
-        <v>91.18000000000001</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1111,16 +1078,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G7">
-        <v>89.29000000000001</v>
+        <v>92.86</v>
       </c>
       <c r="H7">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -1130,7 +1097,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1168,10 +1135,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1191,10 +1158,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1208,16 +1175,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920021</v>
+        <v>20330051920060</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1231,22 +1198,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920060</v>
+        <v>20330051920040</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1254,16 +1221,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920040</v>
+        <v>20330051920046</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1277,16 +1244,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920046</v>
+        <v>20330051920365</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1300,16 +1267,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920365</v>
+        <v>20330051920111</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1323,19 +1290,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920058</v>
+        <v>20330051920112</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
         <v>15</v>
@@ -1346,139 +1313,24 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920111</v>
+        <v>21330051920028</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920112</v>
-      </c>
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" t="s">
-        <v>58</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920028</v>
-      </c>
-      <c r="B12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" t="s">
-        <v>59</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920226</v>
-      </c>
-      <c r="B13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" t="s">
-        <v>60</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920240</v>
-      </c>
-      <c r="B14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" t="s">
-        <v>61</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920251</v>
-      </c>
-      <c r="B15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" t="s">
-        <v>62</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Velasco Sánchez David - Estadisticos 20222.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20222.xlsx
@@ -831,16 +831,19 @@
         <v>20</v>
       </c>
       <c r="D5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="H5">
+        <v>7.2</v>
       </c>
     </row>
     <row r="6" spans="1:8">

--- a/docentes/Velasco Sánchez David - Estadisticos 20222.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="45">
   <si>
     <t>Mat</t>
   </si>
@@ -109,9 +109,6 @@
     <t>VASQUEZ</t>
   </si>
   <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
@@ -133,9 +130,6 @@
     <t>GAMEZ</t>
   </si>
   <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
     <t>JOSUE</t>
   </si>
   <si>
@@ -158,9 +152,6 @@
   </si>
   <si>
     <t>GUILLERMO</t>
-  </si>
-  <si>
-    <t>JAFET</t>
   </si>
 </sst>
 </file>
@@ -756,16 +747,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>78.13</v>
+      </c>
+      <c r="H2">
+        <v>6.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -951,16 +945,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>75</v>
+        <v>78.13</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1100,7 +1094,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1138,10 +1132,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1161,10 +1155,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1184,10 +1178,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1207,10 +1201,10 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1230,10 +1224,10 @@
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1253,10 +1247,10 @@
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1276,10 +1270,10 @@
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1299,10 +1293,10 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1312,29 +1306,6 @@
       </c>
       <c r="G9">
         <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920028</v>
-      </c>
-      <c r="B10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Velasco Sánchez David - Estadisticos 20222.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -83,75 +83,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>VINALAY</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>ANGEL SAID</t>
-  </si>
-  <si>
-    <t>FRANCISCO ALAN</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>BRUNO AZAEL</t>
-  </si>
-  <si>
-    <t>ABIUD</t>
-  </si>
-  <si>
-    <t>GUILLERMO</t>
   </si>
 </sst>
 </file>
@@ -971,16 +902,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1023,16 +954,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G5">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1049,16 +980,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G6">
-        <v>71.43000000000001</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>6.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1075,16 +1006,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G7">
-        <v>92.86</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -1094,7 +1025,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1124,190 +1055,6 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>20330051920362</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920013</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920060</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920040</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920046</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920365</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920111</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920112</v>
-      </c>
-      <c r="B9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Velasco Sánchez David - Estadisticos 20222.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -83,6 +83,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
   </si>
 </sst>
 </file>
@@ -1025,7 +1034,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1055,6 +1064,29 @@
         <v>21</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920195</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Velasco Sánchez David - Estadisticos 20222.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -83,15 +83,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
   </si>
 </sst>
 </file>
@@ -885,13 +876,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>78.13</v>
+        <v>81.25</v>
       </c>
       <c r="H2">
         <v>6.8</v>
@@ -1034,7 +1025,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1064,29 +1055,6 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920195</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
